--- a/results/[6_green_friendly]_#_inv_cost.xlsx
+++ b/results/[6_green_friendly]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31251.19287316165</v>
+        <v>89448.59755583976</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>49277.88459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>386830.1019569611</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2317792.09144148</v>
       </c>
       <c r="F2" t="n">
-        <v>75465.07577201782</v>
+        <v>151477.8289362979</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>20274.22343033684</v>
+        <v>20608.36995567114</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>18910.44901441236</v>
+        <v>23946.68098699136</v>
       </c>
       <c r="O2" t="n">
-        <v>15952.10825463477</v>
+        <v>15691.43421415045</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>24677.2233802937</v>
+        <v>563993.9294964683</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1196479.899689134</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>56155.0398571117</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>45281.94202016341</v>
+        <v>44964.50282109582</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>41319.33120982331</v>
+        <v>79832.59882354148</v>
       </c>
       <c r="O2" t="n">
-        <v>34059.82347464918</v>
+        <v>34307.46381310928</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>193961.9401775642</v>
+        <v>389595.7802787601</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>754668.2160649784</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1140.740783696684</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>31499.18821270974</v>
+        <v>31470.23271071272</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21219.57328507274</v>
       </c>
       <c r="N2" t="n">
-        <v>42646.53192577381</v>
+        <v>87079.68672813929</v>
       </c>
       <c r="O2" t="n">
-        <v>24018.47504444163</v>
+        <v>24041.87791734704</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>9262.79801954542</v>
+        <v>10487.01772702384</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1064,10 +1064,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61364.47115330531</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1544.757918726473</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>22517.87701973088</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>6650.12915920241</v>
+        <v>6653.9330005691</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>660177.384549491</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>

--- a/results/[6_green_friendly]_#_inv_cost.xlsx
+++ b/results/[6_green_friendly]_#_inv_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>26325.3230893218</v>
+        <v>89448.59755583976</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>49277.88459670779</v>
       </c>
       <c r="C2" t="n">
-        <v>417051.6887168352</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>2317792.09144148</v>
       </c>
       <c r="F2" t="n">
-        <v>68792.76884578625</v>
+        <v>151477.8289362979</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>21387.67371038613</v>
+        <v>20608.36995567114</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>20541.0926510224</v>
+        <v>23946.68098699136</v>
       </c>
       <c r="O2" t="n">
-        <v>15066.01836713905</v>
+        <v>15691.43421415045</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13641.31026914664</v>
+        <v>563993.9294964683</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1191640.552160383</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>62627.17757555633</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>42508.22439121734</v>
+        <v>44964.50282109582</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>54572.42898948202</v>
+        <v>79832.59882354148</v>
       </c>
       <c r="O2" t="n">
-        <v>27155.87524550967</v>
+        <v>34307.46381310928</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112388.9212775906</v>
+        <v>389595.7802787601</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>893604.4700225672</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>15479.8228544463</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>29654.26283910253</v>
+        <v>31470.23271071272</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>21219.57328507274</v>
       </c>
       <c r="N2" t="n">
-        <v>45026.60623668434</v>
+        <v>87079.68672813929</v>
       </c>
       <c r="O2" t="n">
-        <v>34245.40897230533</v>
+        <v>24041.87791734704</v>
       </c>
     </row>
   </sheetData>
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10487.01772702384</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>6653.9330005691</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>660177.384549491</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
